--- a/data/satisfaction_detail/2026/1-8月/特色美食廊.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/特色美食廊.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.470000000000001</v>
+        <v>9.372008639308854</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.824067674586033</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.310878329733622</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.720000000000001</v>
+        <v>9.739942404607632</v>
       </c>
     </row>
     <row r="4">
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.039999999999999</v>
+        <v>9.054154067674586</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.735925125989922</v>
       </c>
     </row>
     <row r="5">
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>8.69</v>
+        <v>8.695968322534197</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.550000000000001</v>
+        <v>9.588596112311015</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.823671706263498</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.59</v>
+        <v>9.601022318214543</v>
       </c>
     </row>
     <row r="7">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.57</v>
+        <v>9.569186465082794</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.73</v>
+        <v>9.756688264938806</v>
       </c>
     </row>
     <row r="8">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.828653707703385</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.82</v>
+        <v>9.845788336933046</v>
       </c>
     </row>
     <row r="9">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.42</v>
+        <v>9.426090712742981</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.74</v>
+        <v>9.753981281497481</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.75</v>
+        <v>9.782174226061915</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.894413246940244</v>
       </c>
     </row>
     <row r="11">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9.119999999999999</v>
+        <v>9.294550035997121</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9.67</v>
+        <v>9.800647948164146</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.318905687544996</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.470000000000001</v>
+        <v>9.83245122985581</v>
       </c>
     </row>
     <row r="13">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.48</v>
+        <v>9.478819294456443</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.810727141828654</v>
       </c>
     </row>
     <row r="14">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.08</v>
+        <v>9.087717782577394</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.74</v>
+        <v>9.742102231821455</v>
       </c>
     </row>
     <row r="15">
